--- a/src/daily-report/monitoring-data/06032026.xlsx
+++ b/src/daily-report/monitoring-data/06032026.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="177" documentId="11_60CB878D9B627CC6D1A2A7C718BDEA919AC71CBF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BBF9057-51F1-44D5-B1DE-47DA1E0365AE}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmy/dev/bobs/R&amp;M/2026/7-12/BE-14560/MonitoringData/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A15CCA3-2056-CD43-BB4C-4A96504BF93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="10" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="23400" windowHeight="11720" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dynatrace" sheetId="4" r:id="rId1"/>
@@ -376,9 +381,6 @@
     <t>SalesFeed</t>
   </si>
   <si>
-    <t>Success</t>
-  </si>
-  <si>
     <t>Date/Time</t>
   </si>
   <si>
@@ -485,6 +487,9 @@
   </si>
   <si>
     <t>https://pagespeed.web.dev/analysis/https-www-mybobs-com-furniture-living-room-living-room-sets-p-20065453/v5h8q24hyu?form_factor=desktop</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
 </sst>
 </file>
@@ -556,11 +561,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -929,9 +936,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -969,7 +976,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1075,7 +1082,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1217,7 +1224,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1226,9 +1233,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D8F103-07F9-4E6B-B5F5-8DC920550397}">
   <dimension ref="A1:AZ16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:52" ht="40.5">
+    <row r="1" spans="1:52" ht="45">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -2132,47 +2139,47 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF0A035-8A44-4652-8F19-54DD955ED558}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="60.75">
+    <row r="1" spans="1:12" ht="64">
       <c r="A1" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="C1" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="D1" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="E1" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="F1" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="G1" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="H1" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="I1" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="J1" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="J1" s="55" t="s">
+      <c r="K1" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="K1" s="55" t="s">
+      <c r="L1" s="56" t="s">
         <v>122</v>
-      </c>
-      <c r="L1" s="56" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2180,7 +2187,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2" s="31">
         <v>22</v>
@@ -2215,7 +2222,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="31">
         <v>34</v>
@@ -2250,7 +2257,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="31">
         <v>25</v>
@@ -2285,7 +2292,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="31">
         <v>31</v>
@@ -2320,7 +2327,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6" s="31">
         <v>11</v>
@@ -2355,7 +2362,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" s="31">
         <v>21</v>
@@ -2390,7 +2397,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="38">
         <v>11</v>
@@ -2425,7 +2432,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="31">
         <v>24</v>
@@ -2460,7 +2467,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="31">
         <v>25</v>
@@ -2495,7 +2502,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="31">
         <v>11</v>
@@ -2530,7 +2537,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="31">
         <v>23</v>
@@ -2565,7 +2572,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" s="38">
         <v>7</v>
@@ -2600,7 +2607,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14" s="31">
         <v>25</v>
@@ -2630,7 +2637,7 @@
         <v>15</v>
       </c>
       <c r="L14" s="58" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2638,7 +2645,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C15" s="31">
         <v>32</v>
@@ -2668,7 +2675,7 @@
         <v>6</v>
       </c>
       <c r="L15" s="58" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2676,7 +2683,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C16" s="31">
         <v>21</v>
@@ -2706,7 +2713,7 @@
         <v>15.8</v>
       </c>
       <c r="L16" s="58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2714,7 +2721,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C17" s="31">
         <v>28</v>
@@ -2744,7 +2751,7 @@
         <v>6.9</v>
       </c>
       <c r="L17" s="58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2752,7 +2759,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" s="31">
         <v>8</v>
@@ -2782,7 +2789,7 @@
         <v>13.3</v>
       </c>
       <c r="L18" s="58" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2790,7 +2797,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C19" s="31">
         <v>20</v>
@@ -2820,7 +2827,7 @@
         <v>5.3</v>
       </c>
       <c r="L19" s="58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2828,7 +2835,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C20" s="31">
         <v>8</v>
@@ -2858,7 +2865,7 @@
         <v>14</v>
       </c>
       <c r="L20" s="58" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2866,7 +2873,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C21" s="31">
         <v>24</v>
@@ -2896,7 +2903,7 @@
         <v>5.4</v>
       </c>
       <c r="L21" s="58" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2904,7 +2911,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C22" s="31">
         <v>23</v>
@@ -2934,7 +2941,7 @@
         <v>16.7</v>
       </c>
       <c r="L22" s="58" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2942,7 +2949,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C23" s="31">
         <v>11</v>
@@ -2972,7 +2979,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="L23" s="58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2980,7 +2987,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C24" s="31">
         <v>25</v>
@@ -3010,7 +3017,7 @@
         <v>21.3</v>
       </c>
       <c r="L24" s="58" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -3018,7 +3025,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="31">
         <v>13</v>
@@ -3048,7 +3055,7 @@
         <v>7.3</v>
       </c>
       <c r="L25" s="58" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -3073,44 +3080,44 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1977238C-3335-460B-B697-16E4DB6A05C3}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="C1" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="D1" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="E1" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="F1" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="G1" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="H1" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="I1" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="J1" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="J1" s="54" t="s">
+      <c r="K1" s="54" t="s">
         <v>121</v>
-      </c>
-      <c r="K1" s="54" t="s">
-        <v>122</v>
       </c>
       <c r="L1" s="56"/>
     </row>
@@ -3119,7 +3126,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2">
         <v>43</v>
@@ -3154,7 +3161,7 @@
         <v>46176.541666666664</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3">
         <v>56</v>
@@ -3189,7 +3196,7 @@
         <v>46176.541666608799</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4">
         <v>47</v>
@@ -3224,7 +3231,7 @@
         <v>46176.541666608799</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5">
         <v>55</v>
@@ -3259,7 +3266,7 @@
         <v>46176.541666608799</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6">
         <v>49</v>
@@ -3294,7 +3301,7 @@
         <v>46176.541666608799</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7">
         <v>48</v>
@@ -3329,7 +3336,7 @@
         <v>46176.541666608799</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8">
         <v>48</v>
@@ -3364,7 +3371,7 @@
         <v>46176.541666608799</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9">
         <v>48</v>
@@ -3399,7 +3406,7 @@
         <v>46176.541666608799</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10">
         <v>24</v>
@@ -3434,7 +3441,7 @@
         <v>46176.541666608799</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11">
         <v>19</v>
@@ -3469,7 +3476,7 @@
         <v>46176.541666608799</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12">
         <v>25</v>
@@ -3504,7 +3511,7 @@
         <v>46176.541666608799</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -3539,7 +3546,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C14">
         <v>21</v>
@@ -3574,7 +3581,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C15">
         <v>27</v>
@@ -3609,7 +3616,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C16">
         <v>24</v>
@@ -3644,7 +3651,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C17">
         <v>31</v>
@@ -3679,7 +3686,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18">
         <v>23</v>
@@ -3714,7 +3721,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C19">
         <v>35</v>
@@ -3749,7 +3756,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C20">
         <v>23</v>
@@ -3784,7 +3791,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C21">
         <v>25</v>
@@ -3819,7 +3826,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C22">
         <v>24</v>
@@ -3854,7 +3861,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C23">
         <v>25</v>
@@ -3889,7 +3896,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C24" s="59">
         <v>14</v>
@@ -3924,7 +3931,7 @@
         <v>46176.958333333336</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="59">
         <v>21</v>
@@ -3962,7 +3969,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD59D8F-7862-4586-A284-B01A0AE246AA}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="30" t="s">
@@ -4090,12 +4097,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D68163B8-AB8D-468B-BD18-EEE4732E48D3}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="60.75">
+    <row r="1" spans="1:18" ht="64">
       <c r="A1" s="7" t="s">
         <v>15</v>
       </c>
@@ -4211,10 +4218,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E32B8E4A-D2AD-4B29-A5FF-E4F844794B36}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4247,9 +4254,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{305DEE76-EC68-4504-89D6-160BC1922F4E}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4392,9 +4399,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BB13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:54">
@@ -4636,9 +4643,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB46F41-E4AA-44B0-9106-5F64F47675B6}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="7" width="29.42578125" customWidth="1"/>
+    <col min="1" max="7" width="29.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4794,9 +4801,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F945B554-56C3-4E2E-813A-1A69745AABFD}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="45.75">
+    <row r="1" spans="1:7" ht="48">
       <c r="A1" s="47" t="s">
         <v>15</v>
       </c>
@@ -4885,9 +4892,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F370B5B-7C8E-4F63-9437-B325B376DD7C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="16">
       <c r="A1" s="52" t="s">
         <v>15</v>
       </c>
@@ -4900,7 +4907,7 @@
         <v>45811</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -5144,6 +5151,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6f3914ed-804d-4537-8669-10878f991e94" xsi:nil="true"/>
@@ -5154,23 +5170,40 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F61325C-B8DF-4930-A1E4-D1F37C50376B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F61325C-B8DF-4930-A1E4-D1F37C50376B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="574c0a2a-9be9-44c8-b426-d750bd54aa59"/>
+    <ds:schemaRef ds:uri="6f3914ed-804d-4537-8669-10878f991e94"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4B6FC64-779A-4E4A-AE1C-30A3DF1D6FDC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{101B7E53-1D3F-46C6-8B06-D78AF7DB0CA6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{101B7E53-1D3F-46C6-8B06-D78AF7DB0CA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4B6FC64-779A-4E4A-AE1C-30A3DF1D6FDC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6f3914ed-804d-4537-8669-10878f991e94"/>
+    <ds:schemaRef ds:uri="574c0a2a-9be9-44c8-b426-d750bd54aa59"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/src/daily-report/monitoring-data/06032026.xlsx
+++ b/src/daily-report/monitoring-data/06032026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmy/dev/bobs/R&amp;M/2026/7-12/BE-14560/MonitoringData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A15CCA3-2056-CD43-BB4C-4A96504BF93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90104351-BD17-1B4C-A027-35B202CD96B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="23400" windowHeight="11720" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="32420" windowHeight="11720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dynatrace" sheetId="4" r:id="rId1"/>
@@ -24,6 +24,8 @@
     <sheet name="Bloomreach" sheetId="9" r:id="rId9"/>
     <sheet name="LighthouseProd" sheetId="11" r:id="rId10"/>
     <sheet name="LighthouseS3" sheetId="10" r:id="rId11"/>
+    <sheet name="Blog Page" sheetId="12" r:id="rId12"/>
+    <sheet name="Shoptelligence" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="149">
   <si>
     <t>Problem #</t>
   </si>
@@ -490,6 +492,9 @@
   </si>
   <si>
     <t>Failed</t>
+  </si>
+  <si>
+    <t>Not display</t>
   </si>
 </sst>
 </file>
@@ -3966,6 +3971,58 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442C4A35-42DF-5D4F-8D51-00734945CE32}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16">
+      <c r="A1" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="53">
+        <v>45811</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C282AC-282F-414D-A2A8-C64F681CEE02}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16">
+      <c r="A1" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="53">
+        <v>45811</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD59D8F-7862-4586-A284-B01A0AE246AA}">
   <dimension ref="A1:K10"/>
@@ -4916,6 +4973,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100942D2D4AC09D55439F0B3A4B5486D58B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="49545e226300a70bb41f6bdd36feecd0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="574c0a2a-9be9-44c8-b426-d750bd54aa59" xmlns:ns3="6f3914ed-804d-4537-8669-10878f991e94" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="434dc72c2989358cc002d5c6dea590bf" ns2:_="" ns3:_="">
     <xsd:import namespace="574c0a2a-9be9-44c8-b426-d750bd54aa59"/>
@@ -5150,15 +5216,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5171,6 +5228,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{101B7E53-1D3F-46C6-8B06-D78AF7DB0CA6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F61325C-B8DF-4930-A1E4-D1F37C50376B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5189,14 +5254,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{101B7E53-1D3F-46C6-8B06-D78AF7DB0CA6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4B6FC64-779A-4E4A-AE1C-30A3DF1D6FDC}">
   <ds:schemaRefs>

--- a/src/daily-report/monitoring-data/06032026.xlsx
+++ b/src/daily-report/monitoring-data/06032026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmy/dev/bobs/R&amp;M/2026/7-12/BE-14560/MonitoringData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90104351-BD17-1B4C-A027-35B202CD96B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF426A0-E693-E341-A5E4-993DA8A56CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="32420" windowHeight="11720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="32420" windowHeight="11720" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dynatrace" sheetId="4" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="LighthouseS3" sheetId="10" r:id="rId11"/>
     <sheet name="Blog Page" sheetId="12" r:id="rId12"/>
     <sheet name="Shoptelligence" sheetId="13" r:id="rId13"/>
+    <sheet name="New Issues" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="154">
   <si>
     <t>Problem #</t>
   </si>
@@ -495,6 +496,21 @@
   </si>
   <si>
     <t>Not display</t>
+  </si>
+  <si>
+    <t>Critical (P1)</t>
+  </si>
+  <si>
+    <t>None Active</t>
+  </si>
+  <si>
+    <t>Critical (P2)</t>
+  </si>
+  <si>
+    <t>Major (P3)</t>
+  </si>
+  <si>
+    <t>Severity</t>
   </si>
 </sst>
 </file>
@@ -506,7 +522,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="m/d/yy\ h:mm;@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,6 +615,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF5F5E5A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -764,7 +786,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -922,6 +944,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4023,6 +4049,53 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40B6BF5A-9C67-1741-AF15-AEA51E6BB676}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16">
+      <c r="A1" s="61" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="17">
+      <c r="A2" s="62" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17">
+      <c r="A3" s="62" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17">
+      <c r="A4" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD59D8F-7862-4586-A284-B01A0AE246AA}">
   <dimension ref="A1:K10"/>
@@ -4982,6 +5055,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6f3914ed-804d-4537-8669-10878f991e94" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="574c0a2a-9be9-44c8-b426-d750bd54aa59">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100942D2D4AC09D55439F0B3A4B5486D58B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="49545e226300a70bb41f6bdd36feecd0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="574c0a2a-9be9-44c8-b426-d750bd54aa59" xmlns:ns3="6f3914ed-804d-4537-8669-10878f991e94" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="434dc72c2989358cc002d5c6dea590bf" ns2:_="" ns3:_="">
     <xsd:import namespace="574c0a2a-9be9-44c8-b426-d750bd54aa59"/>
@@ -5216,17 +5300,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6f3914ed-804d-4537-8669-10878f991e94" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="574c0a2a-9be9-44c8-b426-d750bd54aa59">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{101B7E53-1D3F-46C6-8B06-D78AF7DB0CA6}">
   <ds:schemaRefs>
@@ -5236,6 +5309,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4B6FC64-779A-4E4A-AE1C-30A3DF1D6FDC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6f3914ed-804d-4537-8669-10878f991e94"/>
+    <ds:schemaRef ds:uri="574c0a2a-9be9-44c8-b426-d750bd54aa59"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F61325C-B8DF-4930-A1E4-D1F37C50376B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5252,15 +5336,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4B6FC64-779A-4E4A-AE1C-30A3DF1D6FDC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6f3914ed-804d-4537-8669-10878f991e94"/>
-    <ds:schemaRef ds:uri="574c0a2a-9be9-44c8-b426-d750bd54aa59"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>